--- a/فيزياء ترم اول.xlsx
+++ b/فيزياء ترم اول.xlsx
@@ -2900,13 +2900,13 @@
         <v>14</v>
       </c>
       <c r="I9">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J9">
         <v>24</v>
       </c>
       <c r="K9">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -5999,10 +5999,10 @@
         <v>30</v>
       </c>
       <c r="J3">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K3">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4">
